--- a/Sajjad data/by_country_and_state/USA/NM.xlsx
+++ b/Sajjad data/by_country_and_state/USA/NM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="280">
   <si>
     <t>Business Name</t>
   </si>
@@ -224,6 +224,633 @@
   </si>
   <si>
     <t>2026-10-24T23:06:38.483Z</t>
+  </si>
+  <si>
+    <t>Denture Care of Albuquerque</t>
+  </si>
+  <si>
+    <t>(505) 439-7025</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>3100 San Mateo Blvd NE, Albuquerque, NM 87110</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–6 PM; Sunday8 AM–5 PM; Monday8 AM–8 PM; Tuesday8 AM–8 PM; Wednesday8 AM–8 PM; Thursday8 AM–8 PM; Friday8 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denture+Care+of+Albuquerque/data=!4m7!3m6!1s0x8722752df170ade5:0xa6e8edc73c7e2428!8m2!3d35.1174637!4d-106.5859846!16s%2Fg%2F11rwlwp5s3!19sChIJ5a1w8S11IocRKCR-PMft6KY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:30:53.314Z</t>
+  </si>
+  <si>
+    <t>Sterba Patrick DDS</t>
+  </si>
+  <si>
+    <t>(505) 243-6714</t>
+  </si>
+  <si>
+    <t>606 Encino Pl NE, Albuquerque, NM 87102</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sterba+Patrick+DDS/data=!4m7!3m6!1s0x87220ca6d6cf48f9:0xd4d30d2002770b8!8m2!3d35.0873581!4d-106.6324735!16s%2Fg%2F1tdm45hy!19sChIJ-UjP1qYMIocRuHAnANIwTQ0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:30:56.057Z</t>
+  </si>
+  <si>
+    <t>La Clinica de Familia - Central Medical</t>
+  </si>
+  <si>
+    <t>(575) 528-6400</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>575 S Alameda Blvd, Las Cruces, NM 88005</t>
+  </si>
+  <si>
+    <t>Las Cruces</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/La+Clinica+de+Familia+-+Central+Medical/data=!4m7!3m6!1s0x86de3d86f8c1213f:0xb9ad83c53eef022d!8m2!3d32.305251!4d-106.7794937!16s%2Fg%2F11g8ktcdg0!19sChIJPyHB-IY93oYRLQLvPsWDrbk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:05.587Z</t>
+  </si>
+  <si>
+    <t>Gabaldon Gene a DDS.</t>
+  </si>
+  <si>
+    <t>(575) 521-0306</t>
+  </si>
+  <si>
+    <t>2460 S Locust St Ste C, Las Cruces, NM 88001</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gabaldon+Gene+a+DDS./data=!4m7!3m6!1s0x86de17c1b09f2799:0x53a7e7158d6d552!8m2!3d32.2875551!4d-106.7491401!16s%2Fg%2F1td2vbpc!19sChIJmSefsMEX3oYRUtXWWHF-OgU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:18.882Z</t>
+  </si>
+  <si>
+    <t>La Clinica de Familia - East Mesa Medical / Dental</t>
+  </si>
+  <si>
+    <t>(575) 382-2112</t>
+  </si>
+  <si>
+    <t>Dental clinic</t>
+  </si>
+  <si>
+    <t>8600 Bataan Memorial E, Las Cruces, NM 88011</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/La+Clinica+de+Familia+-+East+Mesa+Medical+%2F+Dental/data=!4m7!3m6!1s0x86de23f547f3b9f9:0x8cf2dac237502d41!8m2!3d32.4061173!4d-106.6518968!16s%2Fg%2F1tk9r6cr!19sChIJ-bnzR_Uj3oYRQS1QN8La8ow?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:31.403Z</t>
+  </si>
+  <si>
+    <t>Hollywood Smiles USA.</t>
+  </si>
+  <si>
+    <t>(575) 526-3066</t>
+  </si>
+  <si>
+    <t>808 Spruce Ave, Las Cruces, NM 88001</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hollywood+Smiles+USA./data=!4m7!3m6!1s0x86de3d9e0ce3c9ad:0xf68d70c974db692b!8m2!3d32.320113!4d-106.7723994!16s%2Fg%2F1td6sp5f!19sChIJrcnjDJ493oYRK2nbdMlwjfY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:48.802Z</t>
+  </si>
+  <si>
+    <t>Trigo &amp; Trigo</t>
+  </si>
+  <si>
+    <t>(575) 521-7017</t>
+  </si>
+  <si>
+    <t>1131 Med Park Dr, Las Cruces, NM 88005</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trigo+%26+Trigo/data=!4m7!3m6!1s0x86de16294079e3f9:0xb66c04e447604975!8m2!3d32.2979192!4d-106.777766!16s%2Fg%2F113jrm793!19sChIJ-eN5QCkW3oYRdUlgR-QEbLY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:51.358Z</t>
+  </si>
+  <si>
+    <t>Natalie Ortiz</t>
+  </si>
+  <si>
+    <t>(575) 521-8720</t>
+  </si>
+  <si>
+    <t>3045 E University Ave Ste B, Las Cruces, NM 88011</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Natalie+Ortiz/data=!4m7!3m6!1s0x86de17ed9ddeaaab:0x42d5b6141d43cec3!8m2!3d32.288757!4d-106.7363412!16s%2Fg%2F11qgb7kznm!19sChIJq6rene0X3oYRw85DHRS21UI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:33:04.026Z</t>
+  </si>
+  <si>
+    <t>Dr. Gustavo Sida</t>
+  </si>
+  <si>
+    <t>(575) 541-5941</t>
+  </si>
+  <si>
+    <t>1998 Motel Blvd Bldg A, Las Cruces, NM 88007</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gustavo+Sida/data=!4m7!3m6!1s0x86de3ddc08ec2a4d:0xc9389c1343a6e76b!8m2!3d32.3250692!4d-106.8111193!16s%2Fg%2F11p079_fbv!19sChIJTSrsCNw93oYRa-emQxOcOMk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:33:34.551Z</t>
+  </si>
+  <si>
+    <t>Hayes Peter DDS</t>
+  </si>
+  <si>
+    <t>(575) 382-9292</t>
+  </si>
+  <si>
+    <t>1600 Thorpe Rd, Las Cruces, NM 88012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hayes+Peter+DDS/data=!4m7!3m6!1s0x86de3bf757e7b389:0xf9ebc680b718f8f9!8m2!3d32.3913667!4d-106.8057094!16s%2Fg%2F1wv_snq9!19sChIJibPnV_c73oYR-fgYt4DG6_k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:16.915Z</t>
+  </si>
+  <si>
+    <t>Mc Elmurry Ralph E DDS</t>
+  </si>
+  <si>
+    <t>(575) 522-2477</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>2918 Hillrise Dr, Las Cruces, NM 88011</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mc+Elmurry+Ralph+E+DDS/data=!4m7!3m6!1s0x86de17e316e72dd7:0x66785d9c9feacc58!8m2!3d32.3042271!4d-106.7366615!16s%2Fg%2F1tdr8mrm!19sChIJ1y3nFuMX3oYRWMzqn5xdeGY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:46.667Z</t>
+  </si>
+  <si>
+    <t>Dr. Wendy Lara</t>
+  </si>
+  <si>
+    <t>(505) 521-0127</t>
+  </si>
+  <si>
+    <t>705 E University Ave Ste B, Las Cruces, NM 88001</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Wendy+Lara/data=!4m7!3m6!1s0x86de17c830a0b105:0x6beacf5d466e305!8m2!3d32.2835019!4d-106.7610649!16s%2Fg%2F11rwxfnxmy!19sChIJBbGgMMgX3oYRBeNm1PWsvgY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:35:12.865Z</t>
+  </si>
+  <si>
+    <t>Dentista Hispano en Rio Rancho</t>
+  </si>
+  <si>
+    <t>(505) 398-8215</t>
+  </si>
+  <si>
+    <t>4300 Ridgecrest Dr SE, Rio Rancho, NM 87124</t>
+  </si>
+  <si>
+    <t>Rio Rancho</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentista+Hispano+en+Rio+Rancho/data=!4m7!3m6!1s0x87227195a269d9e7:0x89ef28d47df1d9ab!8m2!3d35.2531202!4d-106.6514203!16s%2Fg%2F11nns7d8ny!19sChIJ59lpopVxIocRq9nxfdQo74k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:37:15.683Z</t>
+  </si>
+  <si>
+    <t>Aesthestic Dental Care LLC</t>
+  </si>
+  <si>
+    <t>(505) 892-2010</t>
+  </si>
+  <si>
+    <t>4111 Barbara Loop SE STE D1, Rio Rancho, NM 87124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aesthestic+Dental+Care+LLC/data=!4m7!3m6!1s0x872270e772c04a4f:0xd49bc4c24cc9fd12!8m2!3d35.2356901!4d-106.6539242!16s%2Fg%2F1wbf_w8r!19sChIJT0rAcudwIocREv3JTMLEm9Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:37:28.992Z</t>
+  </si>
+  <si>
+    <t>River West Orthodontics</t>
+  </si>
+  <si>
+    <t>(505) 881-1101</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>1724 Grande Blvd SE, Rio Rancho, NM 87124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/River+West+Orthodontics/data=!4m7!3m6!1s0x872270e244a437c7:0x956ee3241c68ae5b!8m2!3d35.2291885!4d-106.660604!16s%2Fg%2F1260x8bnj!19sChIJxzekROJwIocRW65oHCTjbpU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:03.972Z</t>
+  </si>
+  <si>
+    <t>Laurence J Rogel PC./</t>
+  </si>
+  <si>
+    <t>(505) 863-4863</t>
+  </si>
+  <si>
+    <t>1316 Jackie Rd SE, Rio Rancho, NM 87124</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laurence+J+Rogel+PC.%2F/data=!4m7!3m6!1s0x8724de99c1a01107:0x3342493251993d8d!8m2!3d35.2396296!4d-106.6532665!16s%2Fg%2F1tdks808!19sChIJBxGgwZneJIcRjT2ZUTJJQjM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:31.963Z</t>
+  </si>
+  <si>
+    <t>Riverside Dental Center &amp; Beauty Spa</t>
+  </si>
+  <si>
+    <t>(505) 346-3186</t>
+  </si>
+  <si>
+    <t>dental implants</t>
+  </si>
+  <si>
+    <t>2600 The American Rd SE Ste 230, Rio Rancho, NM 87124</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Riverside+Dental+Center+%26+Beauty+Spa/data=!4m7!3m6!1s0x8722724b08456f2d:0xce48599af1e8dad2!8m2!3d35.2136059!4d-106.6601094!16s%2Fg%2F1tdvvs4d!19sChIJLW9FCEtyIocR0tro8ZpZSM4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:51.580Z</t>
+  </si>
+  <si>
+    <t>Michael Sweeney</t>
+  </si>
+  <si>
+    <t>(505) 892-8211</t>
+  </si>
+  <si>
+    <t>4111 Barbara Loop SE Ste D2, Rio Rancho, NM 87124</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michael+Sweeney/data=!4m7!3m6!1s0x872270e772906943:0x358beb24639ba3d3!8m2!3d35.2356068!4d-106.6540564!16s%2Fg%2F11p07b4wnx!19sChIJQ2mQcudwIocR06ObYyTrizU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:40:19.147Z</t>
+  </si>
+  <si>
+    <t>Dr. Mark Ferrari</t>
+  </si>
+  <si>
+    <t>(505) 890-0858</t>
+  </si>
+  <si>
+    <t>10250 Cottonwood Park NW Ste B, Albuquerque, NM 87114</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mark+Ferrari/data=!4m7!3m6!1s0x8722716a58455555:0x8f02b085893bb05e!8m2!3d35.2039469!4d-106.6547825!16s%2Fg%2F11qgb6yx2s!19sChIJVVVFWGpxIocRXrA7iYWwAo8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:41:08.156Z</t>
+  </si>
+  <si>
+    <t>Dentist Hispano Santa Fe</t>
+  </si>
+  <si>
+    <t>(505) 391-0018</t>
+  </si>
+  <si>
+    <t>66 E San Francisco St #10, Santa Fe, NM 87501</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>Saturday6 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentist+Hispano+Santa+Fe/data=!4m7!3m6!1s0x871851bed8a2e9c3:0xce162a0bad928d7e!8m2!3d35.6865428!4d-105.9389808!16s%2Fg%2F11rfm6bhb7!19sChIJw-mi2L5RGIcRfo2SrQsqFs4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:42:09.207Z</t>
+  </si>
+  <si>
+    <t>Santa Fe Dentista Hispano Familiar</t>
+  </si>
+  <si>
+    <t>(505) 398-8192</t>
+  </si>
+  <si>
+    <t>1330 Cerrillos Rd, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Santa+Fe+Dentista+Hispano+Familiar/data=!4m7!3m6!1s0x871851172f4f99f5:0x87e1b3983613686!8m2!3d35.6714157!4d-105.9627785!16s%2Fg%2F11nns7n9fx!19sChIJ9ZlPLxdRGIcRhjZhgzkbfgg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:13.790Z</t>
+  </si>
+  <si>
+    <t>Superior Dental Laboratory</t>
+  </si>
+  <si>
+    <t>(505) 988-7030</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>1406 Luisa St Ste 5, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Superior+Dental+Laboratory/data=!4m7!3m6!1s0x8718506175917651:0x38bb92ca26033b9d!8m2!3d35.669509!4d-105.9514389!16s%2Fg%2F1tgp17zq!19sChIJUXaRdWFQGIcRnTsDJsqSuzg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:20.534Z</t>
+  </si>
+  <si>
+    <t>Marcy Street Dental</t>
+  </si>
+  <si>
+    <t>(505) 988-4333</t>
+  </si>
+  <si>
+    <t>217 E Marcy St, Santa Fe, NM 87501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marcy+Street+Dental/data=!4m7!3m6!1s0x8718504876b15115:0x2e3dde349d89b9fa!8m2!3d35.6885466!4d-105.9343978!16s%2Fg%2F1262nwwdh!19sChIJFVGxdkhQGIcR-rmJnTTePS4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:27.360Z</t>
+  </si>
+  <si>
+    <t>North Side Dental Clinic</t>
+  </si>
+  <si>
+    <t>(505) 629-4608</t>
+  </si>
+  <si>
+    <t>Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+Side+Dental+Clinic/data=!4m7!3m6!1s0x87185046ff09d00d:0xe42cdcb40b66aeaf!8m2!3d35.6869812!4d-105.9377966!16s%2Fg%2F1tdfckgh!19sChIJDdAJ_0ZQGIcRr65mC7TcLOQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:36.089Z</t>
+  </si>
+  <si>
+    <t>Blooming Smile Clinic</t>
+  </si>
+  <si>
+    <t>(505) 461-6580</t>
+  </si>
+  <si>
+    <t>125117 Lincoln Ave, Santa Fe, NM 87501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Blooming+Smile+Clinic/data=!4m7!3m6!1s0x8718511e100c3b55:0xdaa7df64fb118d6e!8m2!3d35.6890036!4d-105.9378226!16s%2Fg%2F11vzxpby5j!19sChIJVTsMEB5RGIcRbo0R-2Tfp9o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:39.251Z</t>
+  </si>
+  <si>
+    <t>Michael Ray Martin DDS.</t>
+  </si>
+  <si>
+    <t>(505) 438-0756</t>
+  </si>
+  <si>
+    <t>3600 Cerrillos Rd #507, Santa Fe, NM 87507</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michael+Ray+Martin+DDS./data=!4m7!3m6!1s0x87185a4f304b21df:0xe3950a783015f784!8m2!3d35.642685!4d-106.0063966!16s%2Fg%2F1ttyx5vg!19sChIJ3yFLME9aGIcRhPcVMHgKleM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:05.114Z</t>
+  </si>
+  <si>
+    <t>Balderamos L Paul DDS (Specialist)</t>
+  </si>
+  <si>
+    <t>(505) 983-7373</t>
+  </si>
+  <si>
+    <t>Prosthodontist</t>
+  </si>
+  <si>
+    <t>409 St Michaels Dr Unit D, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–4 PM; Tuesday8 AM–4 PM; Wednesday8 AM–4 PM; Thursday8 AM–4 PM; FridayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Balderamos+L+Paul+DDS+%28Specialist%29/data=!4m7!3m6!1s0x871850ee7a056a73:0xb18db8cf0d46864d!8m2!3d35.6552901!4d-105.9393384!16s%2Fg%2F1tfwqf5c!19sChIJc2oFeu5QGIcRTYZGDc-4jbE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:08.379Z</t>
+  </si>
+  <si>
+    <t>E Ronald Trujillo Family Dentistry: Ron Trujillo, DDS</t>
+  </si>
+  <si>
+    <t>(505) 983-7848</t>
+  </si>
+  <si>
+    <t>2050 Botulph Rd Ste c, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/E+Ronald+Trujillo+Family+Dentistry:+Ron+Trujillo,+DDS/data=!4m7!3m6!1s0x8718518f9bd523fd:0x7e2347ff8676921d!8m2!3d35.6555158!4d-105.948506!16s%2Fg%2F1thmfvvf!19sChIJ_SPVm49RGIcRHZJ2hv9HI34?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:27.557Z</t>
+  </si>
+  <si>
+    <t>Dr. Clarice Pick DDS, PC</t>
+  </si>
+  <si>
+    <t>(505) 982-0094</t>
+  </si>
+  <si>
+    <t>125 Siringo Rd, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Clarice+Pick+DDS,+PC/data=!4m7!3m6!1s0x871850910e6cbb51:0x1c484c4bc3bf4fc6!8m2!3d35.6524827!4d-105.9537353!16s%2Fg%2F1tc_llr_!19sChIJUbtsDpFQGIcRxk-_w0tMSBw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:56.060Z</t>
+  </si>
+  <si>
+    <t>Darmitzel Robert E DDS</t>
+  </si>
+  <si>
+    <t>(505) 988-4161</t>
+  </si>
+  <si>
+    <t>1300 Luisa St #6, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Darmitzel+Robert+E+DDS/data=!4m7!3m6!1s0x871850613c29c9af:0x7444b25623721bce!8m2!3d35.6708906!4d-105.9506421!16s%2Fg%2F1th0nc13!19sChIJr8kpPGFQGIcRzhtyI1ayRHQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:00.870Z</t>
+  </si>
+  <si>
+    <t>Stephen Tanner</t>
+  </si>
+  <si>
+    <t>(505) 670-6145</t>
+  </si>
+  <si>
+    <t>444 St Michaels Dr Ste C, Santa Fe, NM 875057674</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stephen+Tanner/data=!4m7!3m6!1s0x871850ed65090bd9:0xb1e6898a0dace361!8m2!3d35.6563974!4d-105.9444556!16s%2Fg%2F11pkfrwm1k!19sChIJ2QsJZe1QGIcRYeOsDYqJ5rE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:04.187Z</t>
+  </si>
+  <si>
+    <t>Anthony W Mayfield, DDS</t>
+  </si>
+  <si>
+    <t>(505) 983-8051</t>
+  </si>
+  <si>
+    <t>1313 Luisa St A, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Anthony+W+Mayfield,+DDS/data=!4m7!3m6!1s0x87185061173e9075:0x1c3c0e1d49bf6175!8m2!3d35.6705698!4d-105.9502637!16s%2Fg%2F1tdgq8p5!19sChIJdZA-F2FQGIcRdWG_SR0OPBw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:07.070Z</t>
+  </si>
+  <si>
+    <t>Ortega David J DDS.</t>
+  </si>
+  <si>
+    <t>(505) 984-0881</t>
+  </si>
+  <si>
+    <t>550 St Michaels Dr # B, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ortega+David+J+DDS./data=!4m7!3m6!1s0x8718508dd334c6b3:0x8ee13df2adbcb7ca!8m2!3d35.6583496!4d-105.9522703!16s%2Fg%2F1thvyr4n!19sChIJs8Y0041QGIcRyre8rfI94Y4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:09.402Z</t>
+  </si>
+  <si>
+    <t>Gonzales Dental Laboratory</t>
+  </si>
+  <si>
+    <t>(505) 983-7532</t>
+  </si>
+  <si>
+    <t>1402 2nd St, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gonzales+Dental+Laboratory/data=!4m7!3m6!1s0x8718507f8504159f:0xae51fa4cf9239c31!8m2!3d35.6664136!4d-105.9694267!16s%2Fg%2F1td189bx!19sChIJnxUEhX9QGIcRMZwj-Uz6Ua4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:26.269Z</t>
+  </si>
+  <si>
+    <t>Lumident Implant and Surgical Center</t>
+  </si>
+  <si>
+    <t>(505) 308-2055</t>
+  </si>
+  <si>
+    <t>2019 Galisteo St Ste H3, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lumident+Implant+and+Surgical+Center/data=!4m7!3m6!1s0x871851afe3af4809:0x4cc27161d5b54a4c!8m2!3d35.6563408!4d-105.9523195!16s%2Fg%2F11t57mshbz!19sChIJCUiv469RGIcRTEq11WFxwkw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:35.807Z</t>
+  </si>
+  <si>
+    <t>Spier Christopher DDS</t>
+  </si>
+  <si>
+    <t>(505) 988-5194</t>
+  </si>
+  <si>
+    <t>409 Botulph Ln, Santa Fe, NM 87505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Spier+Christopher+DDS/data=!4m7!3m6!1s0x871850928035fe07:0x309520b3ab488b14!8m2!3d35.656273!4d-105.9493341!16s%2Fg%2F1tdx94nv!19sChIJB_41gJJQGIcRFItIq7MglTA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:46:56.572Z</t>
   </si>
 </sst>
 </file>
@@ -604,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -990,6 +1617,1482 @@
         <v>70</v>
       </c>
     </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>113</v>
+      </c>
+      <c r="M16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>124</v>
+      </c>
+      <c r="M18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>129</v>
+      </c>
+      <c r="M19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>136</v>
+      </c>
+      <c r="M20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>147</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>148</v>
+      </c>
+      <c r="M22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>153</v>
+      </c>
+      <c r="M23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>164</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>165</v>
+      </c>
+      <c r="M25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>171</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>177</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>178</v>
+      </c>
+      <c r="M27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>118</v>
+      </c>
+      <c r="I28" t="s">
+        <v>183</v>
+      </c>
+      <c r="J28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>184</v>
+      </c>
+      <c r="M28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>190</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>191</v>
+      </c>
+      <c r="M29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>147</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>196</v>
+      </c>
+      <c r="M30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>202</v>
+      </c>
+      <c r="M31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>118</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>207</v>
+      </c>
+      <c r="M32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" t="s">
+        <v>51</v>
+      </c>
+      <c r="J34" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>37</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>222</v>
+      </c>
+      <c r="M35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>226</v>
+      </c>
+      <c r="D36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>228</v>
+      </c>
+      <c r="I36" t="s">
+        <v>229</v>
+      </c>
+      <c r="J36" t="s">
+        <v>230</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>231</v>
+      </c>
+      <c r="M36" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" t="s">
+        <v>234</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>228</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>236</v>
+      </c>
+      <c r="M37" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>241</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>242</v>
+      </c>
+      <c r="M38" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>246</v>
+      </c>
+      <c r="E39" t="s">
+        <v>189</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>247</v>
+      </c>
+      <c r="M39" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E40" t="s">
+        <v>189</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>252</v>
+      </c>
+      <c r="M40" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>255</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>256</v>
+      </c>
+      <c r="E41" t="s">
+        <v>189</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>257</v>
+      </c>
+      <c r="M41" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>261</v>
+      </c>
+      <c r="E42" t="s">
+        <v>189</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>262</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>37</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>263</v>
+      </c>
+      <c r="M42" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>265</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>268</v>
+      </c>
+      <c r="M43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>270</v>
+      </c>
+      <c r="B44" t="s">
+        <v>271</v>
+      </c>
+      <c r="C44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" t="s">
+        <v>272</v>
+      </c>
+      <c r="E44" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>118</v>
+      </c>
+      <c r="I44" t="s">
+        <v>183</v>
+      </c>
+      <c r="J44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>273</v>
+      </c>
+      <c r="M44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>275</v>
+      </c>
+      <c r="B45" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" t="s">
+        <v>189</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>62</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>278</v>
+      </c>
+      <c r="M45" t="s">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
